--- a/artfynd/A 59994-2024 artfynd.xlsx
+++ b/artfynd/A 59994-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>66846931</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587025.0957373444</v>
+        <v>587025</v>
       </c>
       <c r="R2" t="n">
-        <v>6963056.944378433</v>
+        <v>6963057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>66996818</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587061.0080928735</v>
+        <v>587061</v>
       </c>
       <c r="R3" t="n">
-        <v>6963034.085694975</v>
+        <v>6963034</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2017-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>66996819</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587061.0080928735</v>
+        <v>587061</v>
       </c>
       <c r="R4" t="n">
-        <v>6963034.085694975</v>
+        <v>6963034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59994-2024 artfynd.xlsx
+++ b/artfynd/A 59994-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66846931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66996818</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66996819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>